--- a/Convert_from_xlsx_to_Json/table_normalization/education-table10.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/education-table10.xlsx
@@ -241,7 +241,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,12 +251,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,6 +459,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -477,25 +489,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1077,66 +1071,66 @@
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7"/>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="31" t="s">
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="40" t="s">
+      <c r="E2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="40" t="s">
+      <c r="F2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="G2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="40" t="s">
+      <c r="J2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="40" t="s">
+      <c r="K2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="40" t="s">
+      <c r="L2" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="40" t="s">
+      <c r="M2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="40" t="s">
+      <c r="N2" s="31" t="s">
         <v>8</v>
       </c>
       <c r="O2" s="41" t="s">
@@ -1708,55 +1702,55 @@
     <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="30" spans="1:15" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:15" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="39"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="39"/>
     </row>
     <row r="32" spans="1:15" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="40"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="40"/>
+      <c r="M32" s="40"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="40"/>
     </row>
     <row r="33" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35"/>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="35"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
     </row>
     <row r="34" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="22"/>
@@ -1776,49 +1770,49 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="36"/>
+      <c r="A35" s="33"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="33"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
     </row>
     <row r="36" spans="1:16" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
-      <c r="K36" s="37"/>
-      <c r="L36" s="37"/>
-      <c r="M36" s="37"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="37"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
     </row>
     <row r="37" spans="1:16" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35"/>
-      <c r="B37" s="35"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
@@ -1827,55 +1821,55 @@
       <c r="O37" s="29"/>
     </row>
     <row r="38" spans="1:16" s="5" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="38"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="38"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="38"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
     </row>
     <row r="39" spans="1:16" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="39"/>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="39"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="36"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
     </row>
     <row r="40" spans="1:16" s="5" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="32"/>
       <c r="P40" s="30"/>
     </row>
     <row r="41" spans="1:16" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1897,17 +1891,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="A32:O32"/>
+    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A40:O40"/>
     <mergeCell ref="A35:O35"/>
     <mergeCell ref="A36:O36"/>
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:O38"/>
     <mergeCell ref="A39:O39"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="I1:O1"/>
-    <mergeCell ref="A31:O31"/>
-    <mergeCell ref="A32:O32"/>
-    <mergeCell ref="A33:O33"/>
   </mergeCells>
   <pageMargins left="0.39370078740157499" right="0.47244094488188998" top="0.98425196850393704" bottom="0.98425196850393704" header="0.47244094488188998" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="58" orientation="landscape"/>
